--- a/uploads/TPH BLISS.xlsx
+++ b/uploads/TPH BLISS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="302">
   <si>
     <t>9910031308</t>
   </si>
@@ -940,12 +940,16 @@
   </si>
   <si>
     <t>Kajal Mugrai</t>
+  </si>
+  <si>
+    <t>ddfgfg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1302,9 +1306,9 @@
   <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="224.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="66.5703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="224.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
@@ -1367,7 +1371,9 @@
       <c r="B6" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
